--- a/all_years.xlsx
+++ b/all_years.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509CE914-B0CB-46F4-948E-3E83FF70D8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A43D905-AD34-431E-A623-9768AF9F13A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="1920" yWindow="864" windowWidth="20952" windowHeight="12816" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="10" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>kaikki ottelut</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t>2025-2027</t>
+  </si>
+  <si>
+    <t>15,23,14</t>
   </si>
 </sst>
 </file>
@@ -496,28 +499,28 @@
       <sheetData sheetId="0">
         <row r="5">
           <cell r="C5">
-            <v>63</v>
+            <v>72</v>
           </cell>
           <cell r="D5">
-            <v>29</v>
+            <v>33</v>
           </cell>
           <cell r="E5">
             <v>7</v>
           </cell>
           <cell r="F5">
-            <v>27</v>
+            <v>32</v>
           </cell>
           <cell r="G5">
-            <v>66</v>
+            <v>74</v>
           </cell>
           <cell r="H5">
-            <v>62</v>
+            <v>72</v>
           </cell>
           <cell r="I5">
-            <v>3043</v>
+            <v>3460</v>
           </cell>
           <cell r="J5">
-            <v>3034</v>
+            <v>3480</v>
           </cell>
         </row>
       </sheetData>
@@ -543,10 +546,10 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="C4">
-            <v>11</v>
+            <v>16</v>
           </cell>
           <cell r="D4">
-            <v>4</v>
+            <v>9</v>
           </cell>
           <cell r="E4">
             <v>0</v>
@@ -555,16 +558,16 @@
             <v>7</v>
           </cell>
           <cell r="G4">
-            <v>9</v>
+            <v>21</v>
           </cell>
           <cell r="H4">
             <v>15</v>
           </cell>
           <cell r="I4">
-            <v>544</v>
+            <v>847</v>
           </cell>
           <cell r="J4">
-            <v>580</v>
+            <v>796</v>
           </cell>
         </row>
       </sheetData>
@@ -588,26 +591,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="C2">
-            <v>11</v>
+            <v>18</v>
           </cell>
           <cell r="D2">
-            <v>4</v>
+            <v>5</v>
           </cell>
           <cell r="E2"/>
           <cell r="F2">
-            <v>7</v>
+            <v>13</v>
           </cell>
           <cell r="G2">
-            <v>14</v>
+            <v>16</v>
           </cell>
           <cell r="H2">
-            <v>19</v>
+            <v>38</v>
           </cell>
           <cell r="I2">
-            <v>940</v>
+            <v>1414</v>
           </cell>
           <cell r="J2">
-            <v>1007</v>
+            <v>1595</v>
           </cell>
         </row>
       </sheetData>
@@ -625,6 +628,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="powercup"/>
+      <sheetName val="2026"/>
       <sheetName val="2025"/>
       <sheetName val="2024"/>
       <sheetName val="2023"/>
@@ -667,6 +671,7 @@
       <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
       <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1217,11 +1222,11 @@
       </c>
       <c r="C6" s="4">
         <f>'[4]B 2023-2026'!$C$5</f>
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D6" s="4">
         <f>'[4]B 2023-2026'!$D$5</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E6" s="4">
         <f>'[4]B 2023-2026'!$E$5</f>
@@ -1229,26 +1234,26 @@
       </c>
       <c r="F6" s="4">
         <f>'[4]B 2023-2026'!$F$5</f>
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G6" s="4">
         <f>'[4]B 2023-2026'!$G$5</f>
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H6" s="4">
         <f>'[4]B 2023-2026'!$H$5</f>
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="I6" s="4">
         <f>'[4]B 2023-2026'!$I$5</f>
-        <v>3043</v>
+        <v>3460</v>
       </c>
       <c r="J6" s="4">
         <f>'[4]B 2023-2026'!$J$5</f>
-        <v>3034</v>
-      </c>
-      <c r="K6" s="4">
-        <v>15.23</v>
+        <v>3480</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -1260,11 +1265,11 @@
       </c>
       <c r="C7" s="5">
         <f>'[5]A 2025-2027'!$C$4</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D7" s="5">
         <f>'[5]A 2025-2027'!$D$4</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E7" s="5">
         <f>'[5]A 2025-2027'!$E$4</f>
@@ -1276,7 +1281,7 @@
       </c>
       <c r="G7" s="5">
         <f>'[5]A 2025-2027'!$G$4</f>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H7" s="5">
         <f>'[5]A 2025-2027'!$H$4</f>
@@ -1284,11 +1289,11 @@
       </c>
       <c r="I7" s="5">
         <f>'[5]A 2025-2027'!$I$4</f>
-        <v>544</v>
+        <v>847</v>
       </c>
       <c r="J7" s="5">
         <f>'[5]A 2025-2027'!$J$4</f>
-        <v>580</v>
+        <v>796</v>
       </c>
       <c r="K7" s="5"/>
     </row>
@@ -1301,11 +1306,11 @@
       </c>
       <c r="C8" s="4">
         <f>'[6]M2 2025-2027'!$C$2</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D8" s="4">
         <f>'[6]M2 2025-2027'!$D$2</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="4">
         <f>'[6]M2 2025-2027'!$E$2</f>
@@ -1313,23 +1318,23 @@
       </c>
       <c r="F8" s="4">
         <f>'[6]M2 2025-2027'!$F$2</f>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G8" s="4">
         <f>'[6]M2 2025-2027'!$G$2</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H8" s="4">
         <f>'[6]M2 2025-2027'!$H$2</f>
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="I8" s="4">
         <f>'[6]M2 2025-2027'!$I$2</f>
-        <v>940</v>
+        <v>1414</v>
       </c>
       <c r="J8" s="4">
         <f>'[6]M2 2025-2027'!$J$2</f>
-        <v>1007</v>
+        <v>1595</v>
       </c>
       <c r="K8" s="4"/>
     </row>
@@ -1340,11 +1345,11 @@
       <c r="B9" s="5"/>
       <c r="C9" s="7">
         <f>SUM(C2:C8)</f>
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" ref="D9:J9" si="0">SUM(D2:D8)</f>
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" si="0"/>
@@ -1352,23 +1357,23 @@
       </c>
       <c r="F9" s="7">
         <f t="shared" si="0"/>
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="G9" s="7">
         <f t="shared" si="0"/>
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="H9" s="7">
         <f t="shared" si="0"/>
-        <v>371</v>
+        <v>400</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="0"/>
-        <v>19144</v>
+        <v>20338</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="0"/>
-        <v>18215</v>
+        <v>19465</v>
       </c>
       <c r="K9" s="5"/>
     </row>
@@ -1479,11 +1484,11 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4">
         <f>SUM(C9:C12)</f>
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" ref="D14:J14" si="1">SUM(D9:D12)</f>
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E14" s="4">
         <f t="shared" si="1"/>
@@ -1491,23 +1496,23 @@
       </c>
       <c r="F14" s="4">
         <f t="shared" si="1"/>
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="1"/>
-        <v>371</v>
+        <v>400</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="1"/>
-        <v>20281</v>
+        <v>21475</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="1"/>
-        <v>19480</v>
+        <v>20730</v>
       </c>
       <c r="K14" s="4"/>
     </row>

--- a/all_years.xlsx
+++ b/all_years.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A43D905-AD34-431E-A623-9768AF9F13A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1EE35A-1FFE-45AB-A561-719FEBE3DF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="864" windowWidth="20952" windowHeight="12816" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
@@ -247,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -272,6 +272,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -546,28 +549,28 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="C4">
-            <v>16</v>
+            <v>19</v>
           </cell>
           <cell r="D4">
-            <v>9</v>
+            <v>10</v>
           </cell>
           <cell r="E4">
             <v>0</v>
           </cell>
           <cell r="F4">
-            <v>7</v>
+            <v>9</v>
           </cell>
           <cell r="G4">
-            <v>21</v>
+            <v>23</v>
           </cell>
           <cell r="H4">
-            <v>15</v>
+            <v>19</v>
           </cell>
           <cell r="I4">
-            <v>847</v>
+            <v>973</v>
           </cell>
           <cell r="J4">
-            <v>796</v>
+            <v>943</v>
           </cell>
         </row>
       </sheetData>
@@ -1265,11 +1268,11 @@
       </c>
       <c r="C7" s="5">
         <f>'[5]A 2025-2027'!$C$4</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D7" s="5">
         <f>'[5]A 2025-2027'!$D$4</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" s="5">
         <f>'[5]A 2025-2027'!$E$4</f>
@@ -1277,25 +1280,27 @@
       </c>
       <c r="F7" s="5">
         <f>'[5]A 2025-2027'!$F$4</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G7" s="5">
         <f>'[5]A 2025-2027'!$G$4</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H7" s="5">
         <f>'[5]A 2025-2027'!$H$4</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5">
         <f>'[5]A 2025-2027'!$I$4</f>
-        <v>847</v>
+        <v>973</v>
       </c>
       <c r="J7" s="5">
         <f>'[5]A 2025-2027'!$J$4</f>
-        <v>796</v>
-      </c>
-      <c r="K7" s="5"/>
+        <v>943</v>
+      </c>
+      <c r="K7" s="9">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
@@ -1345,11 +1350,11 @@
       <c r="B9" s="5"/>
       <c r="C9" s="7">
         <f>SUM(C2:C8)</f>
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D9" s="7">
         <f t="shared" ref="D9:J9" si="0">SUM(D2:D8)</f>
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E9" s="7">
         <f t="shared" si="0"/>
@@ -1357,23 +1362,23 @@
       </c>
       <c r="F9" s="7">
         <f t="shared" si="0"/>
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G9" s="7">
         <f t="shared" si="0"/>
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H9" s="7">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="0"/>
-        <v>20338</v>
+        <v>20464</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="0"/>
-        <v>19465</v>
+        <v>19612</v>
       </c>
       <c r="K9" s="5"/>
     </row>
@@ -1484,11 +1489,11 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4">
         <f>SUM(C9:C12)</f>
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" ref="D14:J14" si="1">SUM(D9:D12)</f>
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E14" s="4">
         <f t="shared" si="1"/>
@@ -1496,23 +1501,23 @@
       </c>
       <c r="F14" s="4">
         <f t="shared" si="1"/>
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="1"/>
-        <v>21475</v>
+        <v>21601</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="1"/>
-        <v>20730</v>
+        <v>20877</v>
       </c>
       <c r="K14" s="4"/>
     </row>

--- a/all_years.xlsx
+++ b/all_years.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E1EE35A-1FFE-45AB-A561-719FEBE3DF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CCF77CF1-DADB-49C5-80E1-2070C58FB0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="864" windowWidth="20952" windowHeight="12816" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="72" yWindow="180" windowWidth="23040" windowHeight="12804" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="10" r:id="rId1"/>
@@ -644,24 +644,24 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="8">
-          <cell r="C8">
-            <v>24</v>
-          </cell>
-          <cell r="D8">
-            <v>9</v>
-          </cell>
-          <cell r="E8">
+        <row r="12">
+          <cell r="C12">
+            <v>179</v>
+          </cell>
+          <cell r="D12">
+            <v>109</v>
+          </cell>
+          <cell r="E12">
             <v>0</v>
           </cell>
-          <cell r="F8">
-            <v>15</v>
-          </cell>
-          <cell r="G8">
-            <v>1137</v>
-          </cell>
-          <cell r="H8">
-            <v>1265</v>
+          <cell r="F12">
+            <v>70</v>
+          </cell>
+          <cell r="G12">
+            <v>8881</v>
+          </cell>
+          <cell r="H12">
+            <v>8297</v>
           </cell>
         </row>
       </sheetData>
@@ -695,12 +695,39 @@
       <sheetName val="U14_2023"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="0">
+        <row r="8">
+          <cell r="C8">
+            <v>66</v>
+          </cell>
+          <cell r="D8">
+            <v>23</v>
+          </cell>
+          <cell r="E8">
+            <v>2</v>
+          </cell>
+          <cell r="F8">
+            <v>41</v>
+          </cell>
+          <cell r="G8">
+            <v>69</v>
+          </cell>
+          <cell r="H8">
+            <v>103</v>
+          </cell>
+          <cell r="I8">
+            <v>2189</v>
+          </cell>
+          <cell r="J8">
+            <v>2372</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1403,30 +1430,36 @@
         <v>27</v>
       </c>
       <c r="C11" s="5">
-        <f>[7]powercup!$C$8</f>
-        <v>24</v>
+        <f>[7]powercup!$C$12</f>
+        <v>179</v>
       </c>
       <c r="D11" s="5">
-        <f>[7]powercup!$D$8</f>
-        <v>9</v>
+        <f>[7]powercup!$D$12</f>
+        <v>109</v>
       </c>
       <c r="E11" s="5">
-        <f>[7]powercup!$E$8</f>
+        <f>[7]powercup!$E$12</f>
         <v>0</v>
       </c>
       <c r="F11" s="5">
-        <f>[7]powercup!$F$8</f>
-        <v>15</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+        <f>[7]powercup!$F$12</f>
+        <v>70</v>
+      </c>
+      <c r="G11" s="5">
+        <f>2*D11</f>
+        <v>218</v>
+      </c>
+      <c r="H11" s="5">
+        <f>2*F11</f>
+        <v>140</v>
+      </c>
       <c r="I11" s="5">
-        <f>[7]powercup!$G$8</f>
-        <v>1137</v>
+        <f>[7]powercup!$G$12</f>
+        <v>8881</v>
       </c>
       <c r="J11" s="5">
-        <f>[7]powercup!$H$8</f>
-        <v>1265</v>
+        <f>[7]powercup!$H$12</f>
+        <v>8297</v>
       </c>
       <c r="K11" s="5"/>
     </row>
@@ -1438,36 +1471,36 @@
         <v>28</v>
       </c>
       <c r="C12" s="4">
-        <f>[8]all!$C$12</f>
-        <v>0</v>
+        <f>[8]all!$C$8</f>
+        <v>66</v>
       </c>
       <c r="D12" s="4">
-        <f>[8]all!$D$12</f>
-        <v>0</v>
+        <f>[8]all!$D$8</f>
+        <v>23</v>
       </c>
       <c r="E12" s="4">
-        <f>[8]all!$E$12</f>
-        <v>0</v>
+        <f>[8]all!$E$8</f>
+        <v>2</v>
       </c>
       <c r="F12" s="4">
-        <f>[8]all!$F$12</f>
-        <v>0</v>
+        <f>[8]all!$F$8</f>
+        <v>41</v>
       </c>
       <c r="G12" s="4">
-        <f>[8]all!$G$12</f>
-        <v>0</v>
+        <f>[8]all!$G$8</f>
+        <v>69</v>
       </c>
       <c r="H12" s="4">
-        <f>[8]all!$H$12</f>
-        <v>0</v>
+        <f>[8]all!$H$8</f>
+        <v>103</v>
       </c>
       <c r="I12" s="4">
-        <f>[8]all!$I$12</f>
-        <v>0</v>
+        <f>[8]all!$I$8</f>
+        <v>2189</v>
       </c>
       <c r="J12" s="4">
-        <f>[8]all!$J$12</f>
-        <v>0</v>
+        <f>[8]all!$J$8</f>
+        <v>2372</v>
       </c>
       <c r="K12" s="4"/>
     </row>
@@ -1489,35 +1522,35 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4">
         <f>SUM(C9:C12)</f>
-        <v>502</v>
+        <v>723</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" ref="D14:J14" si="1">SUM(D9:D12)</f>
-        <v>272</v>
+        <v>395</v>
       </c>
       <c r="E14" s="4">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>316</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>737</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="1"/>
-        <v>404</v>
+        <v>647</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="1"/>
-        <v>21601</v>
+        <v>31534</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="1"/>
-        <v>20877</v>
+        <v>30281</v>
       </c>
       <c r="K14" s="4"/>
     </row>

--- a/all_years.xlsx
+++ b/all_years.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CCF77CF1-DADB-49C5-80E1-2070C58FB0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534EDCBF-8398-4C81-9307-678A6AA56A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="72" yWindow="180" windowWidth="23040" windowHeight="12804" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="0" yWindow="1596" windowWidth="23040" windowHeight="12804" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="10" r:id="rId1"/>
@@ -132,9 +132,6 @@
     <t>2018-2025</t>
   </si>
   <si>
-    <t>2024-2025</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -151,6 +148,9 @@
   </si>
   <si>
     <t>15,23,14</t>
+  </si>
+  <si>
+    <t>2024-2026</t>
   </si>
 </sst>
 </file>
@@ -688,6 +688,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="all"/>
+      <sheetName val="U18_2026"/>
       <sheetName val="U18_2025"/>
       <sheetName val="U16_2025"/>
       <sheetName val="U16_2024"/>
@@ -698,7 +699,7 @@
       <sheetData sheetId="0">
         <row r="8">
           <cell r="C8">
-            <v>66</v>
+            <v>69</v>
           </cell>
           <cell r="D8">
             <v>23</v>
@@ -707,27 +708,28 @@
             <v>2</v>
           </cell>
           <cell r="F8">
-            <v>41</v>
+            <v>44</v>
           </cell>
           <cell r="G8">
             <v>69</v>
           </cell>
           <cell r="H8">
-            <v>103</v>
+            <v>112</v>
           </cell>
           <cell r="I8">
-            <v>2189</v>
+            <v>2267</v>
           </cell>
           <cell r="J8">
-            <v>2372</v>
+            <v>2499</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1248,7 +1250,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="4">
         <f>'[4]B 2023-2026'!$C$5</f>
@@ -1283,15 +1285,15 @@
         <v>3480</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="5">
         <f>'[5]A 2025-2027'!$C$4</f>
@@ -1331,10 +1333,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="C8" s="4">
         <f>'[6]M2 2025-2027'!$C$2</f>
@@ -1468,11 +1470,11 @@
         <v>22</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C12" s="4">
         <f>[8]all!$C$8</f>
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D12" s="4">
         <f>[8]all!$D$8</f>
@@ -1484,7 +1486,7 @@
       </c>
       <c r="F12" s="4">
         <f>[8]all!$F$8</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G12" s="4">
         <f>[8]all!$G$8</f>
@@ -1492,15 +1494,15 @@
       </c>
       <c r="H12" s="4">
         <f>[8]all!$H$8</f>
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I12" s="4">
         <f>[8]all!$I$8</f>
-        <v>2189</v>
+        <v>2267</v>
       </c>
       <c r="J12" s="4">
         <f>[8]all!$J$8</f>
-        <v>2372</v>
+        <v>2499</v>
       </c>
       <c r="K12" s="4"/>
     </row>
@@ -1522,7 +1524,7 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4">
         <f>SUM(C9:C12)</f>
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" ref="D14:J14" si="1">SUM(D9:D12)</f>
@@ -1534,7 +1536,7 @@
       </c>
       <c r="F14" s="4">
         <f t="shared" si="1"/>
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
@@ -1542,15 +1544,15 @@
       </c>
       <c r="H14" s="4">
         <f t="shared" si="1"/>
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="1"/>
-        <v>31534</v>
+        <v>31612</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="1"/>
-        <v>30281</v>
+        <v>30408</v>
       </c>
       <c r="K14" s="4"/>
     </row>

--- a/all_years.xlsx
+++ b/all_years.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\own_prog\github\kaudet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{534EDCBF-8398-4C81-9307-678A6AA56A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86F6680-2F9F-45D3-9DE1-64CA7380FA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1596" windowWidth="23040" windowHeight="12804" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
+    <workbookView xWindow="1968" yWindow="1452" windowWidth="21072" windowHeight="12948" tabRatio="880" xr2:uid="{CFC6D258-5D3C-46F8-BFEC-F3C271445404}"/>
   </bookViews>
   <sheets>
     <sheet name="all" sheetId="10" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>kaikki ottelut</t>
   </si>
@@ -135,12 +135,6 @@
     <t>A</t>
   </si>
   <si>
-    <t>2023-2026</t>
-  </si>
-  <si>
-    <t>2025-2026</t>
-  </si>
-  <si>
     <t>M2</t>
   </si>
   <si>
@@ -151,6 +145,9 @@
   </si>
   <si>
     <t>2024-2026</t>
+  </si>
+  <si>
+    <t>2023-2027</t>
   </si>
 </sst>
 </file>
@@ -493,56 +490,8 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="B 2023-2026"/>
-      <sheetName val="B 2025-2026"/>
-      <sheetName val="B 2024-2025"/>
-      <sheetName val="B 2023-2024"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="5">
-          <cell r="C5">
-            <v>72</v>
-          </cell>
-          <cell r="D5">
-            <v>33</v>
-          </cell>
-          <cell r="E5">
-            <v>7</v>
-          </cell>
-          <cell r="F5">
-            <v>32</v>
-          </cell>
-          <cell r="G5">
-            <v>74</v>
-          </cell>
-          <cell r="H5">
-            <v>72</v>
-          </cell>
-          <cell r="I5">
-            <v>3460</v>
-          </cell>
-          <cell r="J5">
-            <v>3480</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
       <sheetName val="A 2025-2027"/>
+      <sheetName val="A 2026-2027"/>
       <sheetName val="A 2025-2026"/>
     </sheetNames>
     <sheetDataSet>
@@ -575,12 +524,13 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -623,7 +573,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -680,7 +630,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -688,6 +638,7 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="all"/>
+      <sheetName val="JNCT_2026"/>
       <sheetName val="U18_2026"/>
       <sheetName val="U18_2025"/>
       <sheetName val="U16_2025"/>
@@ -699,28 +650,28 @@
       <sheetData sheetId="0">
         <row r="8">
           <cell r="C8">
-            <v>69</v>
+            <v>9</v>
           </cell>
           <cell r="D8">
-            <v>23</v>
+            <v>0</v>
           </cell>
           <cell r="E8">
-            <v>2</v>
+            <v>0</v>
           </cell>
           <cell r="F8">
-            <v>44</v>
+            <v>9</v>
           </cell>
           <cell r="G8">
-            <v>69</v>
+            <v>0</v>
           </cell>
           <cell r="H8">
-            <v>112</v>
+            <v>27</v>
           </cell>
           <cell r="I8">
-            <v>2267</v>
+            <v>260</v>
           </cell>
           <cell r="J8">
-            <v>2499</v>
+            <v>391</v>
           </cell>
         </row>
       </sheetData>
@@ -730,6 +681,58 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="B 2023-2027"/>
+      <sheetName val="B 2026-2027"/>
+      <sheetName val="B 2025-2026"/>
+      <sheetName val="B 2024-2025"/>
+      <sheetName val="B 2023-2024"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="C6">
+            <v>72</v>
+          </cell>
+          <cell r="D6">
+            <v>33</v>
+          </cell>
+          <cell r="E6">
+            <v>7</v>
+          </cell>
+          <cell r="F6">
+            <v>32</v>
+          </cell>
+          <cell r="G6">
+            <v>74</v>
+          </cell>
+          <cell r="H6">
+            <v>1194</v>
+          </cell>
+          <cell r="I6">
+            <v>3460</v>
+          </cell>
+          <cell r="J6">
+            <v>3480</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1250,42 +1253,42 @@
         <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C6" s="4">
-        <f>'[4]B 2023-2026'!$C$5</f>
+        <f>'[8]B 2023-2027'!$C$6</f>
         <v>72</v>
       </c>
       <c r="D6" s="4">
-        <f>'[4]B 2023-2026'!$D$5</f>
+        <f>'[8]B 2023-2027'!$D$6</f>
         <v>33</v>
       </c>
       <c r="E6" s="4">
-        <f>'[4]B 2023-2026'!$E$5</f>
+        <f>'[8]B 2023-2027'!$E$6</f>
         <v>7</v>
       </c>
       <c r="F6" s="4">
-        <f>'[4]B 2023-2026'!$F$5</f>
+        <f>'[8]B 2023-2027'!$F$6</f>
         <v>32</v>
       </c>
       <c r="G6" s="4">
-        <f>'[4]B 2023-2026'!$G$5</f>
+        <f>'[8]B 2023-2027'!$G$6</f>
         <v>74</v>
       </c>
       <c r="H6" s="4">
-        <f>'[4]B 2023-2026'!$H$5</f>
-        <v>72</v>
+        <f>'[8]B 2023-2027'!$H$6</f>
+        <v>1194</v>
       </c>
       <c r="I6" s="4">
-        <f>'[4]B 2023-2026'!$I$5</f>
+        <f>'[8]B 2023-2027'!$I$6</f>
         <v>3460</v>
       </c>
       <c r="J6" s="4">
-        <f>'[4]B 2023-2026'!$J$5</f>
+        <f>'[8]B 2023-2027'!$J$6</f>
         <v>3480</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -1296,35 +1299,35 @@
         <v>30</v>
       </c>
       <c r="C7" s="5">
-        <f>'[5]A 2025-2027'!$C$4</f>
+        <f>'[4]A 2025-2027'!$C$4</f>
         <v>19</v>
       </c>
       <c r="D7" s="5">
-        <f>'[5]A 2025-2027'!$D$4</f>
+        <f>'[4]A 2025-2027'!$D$4</f>
         <v>10</v>
       </c>
       <c r="E7" s="5">
-        <f>'[5]A 2025-2027'!$E$4</f>
+        <f>'[4]A 2025-2027'!$E$4</f>
         <v>0</v>
       </c>
       <c r="F7" s="5">
-        <f>'[5]A 2025-2027'!$F$4</f>
+        <f>'[4]A 2025-2027'!$F$4</f>
         <v>9</v>
       </c>
       <c r="G7" s="5">
-        <f>'[5]A 2025-2027'!$G$4</f>
+        <f>'[4]A 2025-2027'!$G$4</f>
         <v>23</v>
       </c>
       <c r="H7" s="5">
-        <f>'[5]A 2025-2027'!$H$4</f>
+        <f>'[4]A 2025-2027'!$H$4</f>
         <v>19</v>
       </c>
       <c r="I7" s="5">
-        <f>'[5]A 2025-2027'!$I$4</f>
+        <f>'[4]A 2025-2027'!$I$4</f>
         <v>973</v>
       </c>
       <c r="J7" s="5">
-        <f>'[5]A 2025-2027'!$J$4</f>
+        <f>'[4]A 2025-2027'!$J$4</f>
         <v>943</v>
       </c>
       <c r="K7" s="9">
@@ -1333,41 +1336,41 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4">
-        <f>'[6]M2 2025-2027'!$C$2</f>
+        <f>'[5]M2 2025-2027'!$C$2</f>
         <v>18</v>
       </c>
       <c r="D8" s="4">
-        <f>'[6]M2 2025-2027'!$D$2</f>
+        <f>'[5]M2 2025-2027'!$D$2</f>
         <v>5</v>
       </c>
       <c r="E8" s="4">
-        <f>'[6]M2 2025-2027'!$E$2</f>
+        <f>'[5]M2 2025-2027'!$E$2</f>
         <v>0</v>
       </c>
       <c r="F8" s="4">
-        <f>'[6]M2 2025-2027'!$F$2</f>
+        <f>'[5]M2 2025-2027'!$F$2</f>
         <v>13</v>
       </c>
       <c r="G8" s="4">
-        <f>'[6]M2 2025-2027'!$G$2</f>
+        <f>'[5]M2 2025-2027'!$G$2</f>
         <v>16</v>
       </c>
       <c r="H8" s="4">
-        <f>'[6]M2 2025-2027'!$H$2</f>
+        <f>'[5]M2 2025-2027'!$H$2</f>
         <v>38</v>
       </c>
       <c r="I8" s="4">
-        <f>'[6]M2 2025-2027'!$I$2</f>
+        <f>'[5]M2 2025-2027'!$I$2</f>
         <v>1414</v>
       </c>
       <c r="J8" s="4">
-        <f>'[6]M2 2025-2027'!$J$2</f>
+        <f>'[5]M2 2025-2027'!$J$2</f>
         <v>1595</v>
       </c>
       <c r="K8" s="4"/>
@@ -1399,7 +1402,7 @@
       </c>
       <c r="H9" s="7">
         <f t="shared" si="0"/>
-        <v>404</v>
+        <v>1526</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="0"/>
@@ -1432,19 +1435,19 @@
         <v>27</v>
       </c>
       <c r="C11" s="5">
-        <f>[7]powercup!$C$12</f>
+        <f>[6]powercup!$C$12</f>
         <v>179</v>
       </c>
       <c r="D11" s="5">
-        <f>[7]powercup!$D$12</f>
+        <f>[6]powercup!$D$12</f>
         <v>109</v>
       </c>
       <c r="E11" s="5">
-        <f>[7]powercup!$E$12</f>
+        <f>[6]powercup!$E$12</f>
         <v>0</v>
       </c>
       <c r="F11" s="5">
-        <f>[7]powercup!$F$12</f>
+        <f>[6]powercup!$F$12</f>
         <v>70</v>
       </c>
       <c r="G11" s="5">
@@ -1456,11 +1459,11 @@
         <v>140</v>
       </c>
       <c r="I11" s="5">
-        <f>[7]powercup!$G$12</f>
+        <f>[6]powercup!$G$12</f>
         <v>8881</v>
       </c>
       <c r="J11" s="5">
-        <f>[7]powercup!$H$12</f>
+        <f>[6]powercup!$H$12</f>
         <v>8297</v>
       </c>
       <c r="K11" s="5"/>
@@ -1470,39 +1473,39 @@
         <v>22</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" s="4">
-        <f>[8]all!$C$8</f>
-        <v>69</v>
+        <f>[7]all!$C$8</f>
+        <v>9</v>
       </c>
       <c r="D12" s="4">
-        <f>[8]all!$D$8</f>
-        <v>23</v>
+        <f>[7]all!$D$8</f>
+        <v>0</v>
       </c>
       <c r="E12" s="4">
-        <f>[8]all!$E$8</f>
-        <v>2</v>
+        <f>[7]all!$E$8</f>
+        <v>0</v>
       </c>
       <c r="F12" s="4">
-        <f>[8]all!$F$8</f>
-        <v>44</v>
+        <f>[7]all!$F$8</f>
+        <v>9</v>
       </c>
       <c r="G12" s="4">
-        <f>[8]all!$G$8</f>
-        <v>69</v>
+        <f>[7]all!$G$8</f>
+        <v>0</v>
       </c>
       <c r="H12" s="4">
-        <f>[8]all!$H$8</f>
-        <v>112</v>
+        <f>[7]all!$H$8</f>
+        <v>27</v>
       </c>
       <c r="I12" s="4">
-        <f>[8]all!$I$8</f>
-        <v>2267</v>
+        <f>[7]all!$I$8</f>
+        <v>260</v>
       </c>
       <c r="J12" s="4">
-        <f>[8]all!$J$8</f>
-        <v>2499</v>
+        <f>[7]all!$J$8</f>
+        <v>391</v>
       </c>
       <c r="K12" s="4"/>
     </row>
@@ -1524,35 +1527,35 @@
       <c r="B14" s="4"/>
       <c r="C14" s="4">
         <f>SUM(C9:C12)</f>
-        <v>726</v>
+        <v>666</v>
       </c>
       <c r="D14" s="4">
         <f t="shared" ref="D14:J14" si="1">SUM(D9:D12)</f>
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="E14" s="4">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F14" s="4">
         <f t="shared" si="1"/>
-        <v>319</v>
+        <v>284</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>737</v>
+        <v>668</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" si="1"/>
-        <v>656</v>
+        <v>1693</v>
       </c>
       <c r="I14" s="4">
         <f t="shared" si="1"/>
-        <v>31612</v>
+        <v>29605</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="1"/>
-        <v>30408</v>
+        <v>28300</v>
       </c>
       <c r="K14" s="4"/>
     </row>
